--- a/docs/dossiers/dossier-paris-20e-83a9db5d.xlsx
+++ b/docs/dossiers/dossier-paris-20e-83a9db5d.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 13/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 14/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>
@@ -2249,7 +2249,7 @@
       </c>
       <c r="B7" s="29" t="inlineStr">
         <is>
-          <t>Restauration légère possible (sans conduit)</t>
+          <t>Extraction / vraie restauration possible · Restauration légère possible (sans conduit)</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-20e-83a9db5d.xlsx
+++ b/docs/dossiers/dossier-paris-20e-83a9db5d.xlsx
@@ -2309,7 +2309,7 @@
       </c>
       <c r="B12" s="29" t="inlineStr">
         <is>
-          <t>Restauration sans conduit possible</t>
+          <t>3 nouvelles annonces dans votre zone personnalisée : Paris Votre recherche : Vente &gt; Boutique, Local commercial &gt; Paris &gt; Maximum 300,000 € 290 000 € Local commercial 47 m² Paris 20ème arrondissement (75020) Groupe POINTdeVENTE Voir l'annonce 250 000 € Hôtel / Restaurant 67 m² Paris 19ème arrondissement (75019) Groupe POINTdeVENTE Voir l'annonce 122 000 € Hôtel / Restaurant 35 m² Paris 11ème arron</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-20e-83a9db5d.xlsx
+++ b/docs/dossiers/dossier-paris-20e-83a9db5d.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 14/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 15/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-20e-83a9db5d.xlsx
+++ b/docs/dossiers/dossier-paris-20e-83a9db5d.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 15/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 16/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-20e-83a9db5d.xlsx
+++ b/docs/dossiers/dossier-paris-20e-83a9db5d.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 16/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 17/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-20e-83a9db5d.xlsx
+++ b/docs/dossiers/dossier-paris-20e-83a9db5d.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 17/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 18/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-20e-83a9db5d.xlsx
+++ b/docs/dossiers/dossier-paris-20e-83a9db5d.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 18/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 19/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-20e-83a9db5d.xlsx
+++ b/docs/dossiers/dossier-paris-20e-83a9db5d.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 19/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 20/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-20e-83a9db5d.xlsx
+++ b/docs/dossiers/dossier-paris-20e-83a9db5d.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 20/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 21/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-20e-83a9db5d.xlsx
+++ b/docs/dossiers/dossier-paris-20e-83a9db5d.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 21/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 22/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-20e-83a9db5d.xlsx
+++ b/docs/dossiers/dossier-paris-20e-83a9db5d.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 22/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 23/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-20e-83a9db5d.xlsx
+++ b/docs/dossiers/dossier-paris-20e-83a9db5d.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 23/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 24/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-20e-83a9db5d.xlsx
+++ b/docs/dossiers/dossier-paris-20e-83a9db5d.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 24/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 25/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-20e-83a9db5d.xlsx
+++ b/docs/dossiers/dossier-paris-20e-83a9db5d.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 25/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 26/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-20e-83a9db5d.xlsx
+++ b/docs/dossiers/dossier-paris-20e-83a9db5d.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 26/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 27/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="B57" s="15" t="inlineStr">
         <is>
-          <t>77/100</t>
+          <t>72/100</t>
         </is>
       </c>
       <c r="C57" s="18" t="inlineStr">
@@ -2249,7 +2249,7 @@
       </c>
       <c r="B7" s="29" t="inlineStr">
         <is>
-          <t>Extraction / vraie restauration possible · Restauration légère possible (sans conduit)</t>
+          <t>—</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-20e-83a9db5d.xlsx
+++ b/docs/dossiers/dossier-paris-20e-83a9db5d.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 27/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 28/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>
@@ -2249,7 +2249,7 @@
       </c>
       <c r="B7" s="29" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Restauration légère possible (sans conduit)</t>
         </is>
       </c>
     </row>
@@ -2309,7 +2309,7 @@
       </c>
       <c r="B12" s="29" t="inlineStr">
         <is>
-          <t>3 nouvelles annonces dans votre zone personnalisée : Paris Votre recherche : Vente &gt; Boutique, Local commercial &gt; Paris &gt; Maximum 300,000 € 290 000 € Local commercial 47 m² Paris 20ème arrondissement (75020) Groupe POINTdeVENTE Voir l'annonce 250 000 € Hôtel / Restaurant 67 m² Paris 19ème arrondissement (75019) Groupe POINTdeVENTE Voir l'annonce 122 000 € Hôtel / Restaurant 35 m² Paris 11ème arron</t>
+          <t>Restauration sans conduit possible</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-20e-83a9db5d.xlsx
+++ b/docs/dossiers/dossier-paris-20e-83a9db5d.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 28/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 29/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-20e-83a9db5d.xlsx
+++ b/docs/dossiers/dossier-paris-20e-83a9db5d.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 29/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 30/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-20e-83a9db5d.xlsx
+++ b/docs/dossiers/dossier-paris-20e-83a9db5d.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 30/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 31/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>
